--- a/140021设备daily update_20261017.xlsx
+++ b/140021设备daily update_20261017.xlsx
@@ -25,66 +25,66 @@
     <t>Responsible</t>
   </si>
   <si>
-    <t>Progress on 2026/10/18</t>
-  </si>
-  <si>
-    <t>Spray ball installation + coverage test + riboflavin cleaning + particulate check for AT09/AT01
+    <t>Progress as of 2026/10/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spray-ball installation, spray coverage test, riboflavin cleaning test, and particulate inspection for AT09/AT01
 AT09/AT01 的喷淋球安装 + 覆盖性测试 + 核黄素清洗测试 + 微粒检查</t>
   </si>
   <si>
     <t>张忠尧</t>
   </si>
   <si>
-    <t>1. A stainless steel spray ball was used for the spray coverage test on Mixing Vessel AT09. Considering the compatibility issue between iodine and stainless steel, stainless steel cannot remain in the equipment for extended periods. Therefore, the spray ball is only to be used temporarily as an accessory.
-2. Based on customer recommendations and material compatibility considerations, a PTFE spray ball has been procured to replace the existing one for Mixing Vessel AT09. In view of the project timeline, we recommend conducting a trial run and completing the supplementary spray coverage verification and cleaning confirmation prior to using this equipment for the project.
-proposed completion Date: 10/22/2026
-3. Mixing Vessel AT01 was confirmed to be equipped with a spray ball and has undergone spray coverage testing. No hanging identification tag was present on-site, and this nonconformance has been corrected.</t>
+    <t xml:space="preserve">1. A stainless steel spray ball was used for the spray coverage test on mixing vessel AT09. Iodine is not compatible with prolonged stainless-steel contact, so this spray ball will be used only as a temporary accessory and will not remain in the vessel.
+2. A PTFE spray ball has been purchased for mixing vessel AT09, following the client's recommendation and material-compatibility assessment. Given the project timeline, we recommend a trial run and completion of the supplemental spray-coverage verification and cleaning confirmation before this vessel is used for the project.
+Proposed completion date: 10/22/2026
+3. Mixing vessel AT01 is equipped with a spray ball and has completed spray coverage testing. The missing on-site identification tag has been corrected.</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Synthesizer SY16 jacket temperature high-high/low-low alarm addition into PLC
+    <t xml:space="preserve">Addition of high-high and low-low jacket-temperature alarms for synthesizer SY16 to the PLC
  合成器 SY16 夹套温度的高高/低低报警加入 PLC（可编程逻辑控制器)</t>
   </si>
   <si>
     <t>刘亚南</t>
   </si>
   <si>
-    <t>Software development; change document in draft, pending QA review.
-proposed completion Date: 10/21/2026</t>
-  </si>
-  <si>
-    <t>Unused side loop dead legs removal from iodine solution transfer pipeline
+    <t xml:space="preserve">Software development is in progress. The change-control document is in draft and is pending QA review.
+Proposed completion date: 10/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removal of dead legs from unused branches of the iodine-solution transfer line
 去除碘溶液输送管道中未使用支路的死角（dead leg）</t>
   </si>
   <si>
-    <t xml:space="preserve">completed, Remove valve and install blind flange. </t>
-  </si>
-  <si>
-    <t>Iodine solution nitrogen transfer time qualification before solvent run 溶剂运行前，对碘溶液氮气输送时间进行确认（qualification）</t>
-  </si>
-  <si>
-    <t>Iodine solution nitrogen transfer to Synthesizer will be in solvent run.
-proposed completion Date: 10/22/2026</t>
-  </si>
-  <si>
-    <t>Post oxidation DMF cooling time qualification by activation tank in solvent run
+    <t xml:space="preserve">Completed. The valve was removed and a blind flange was installed.</t>
+  </si>
+  <si>
+    <t>Qualification of the iodine-solution nitrogen transfer time before the solvent run 溶剂运行前，对碘溶液氮气输送时间进行确认（qualification）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nitrogen transfer of the iodine solution to the synthesizer will be performed during the solvent run.
+Proposed completion date: 10/22/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualification of post-oxidation DMF cooling time in the activation tank during the solvent run
 溶剂运行中，按活化罐（activation tank）确认氧化后 DMF 的冷却时间</t>
   </si>
   <si>
-    <t>Post oxidation DMF cooling time test by activation tank in solvent run.
-proposed completion Date: 10/22/2026</t>
-  </si>
-  <si>
-    <t>Pre-production equipment train rinse/swab cleanness acceptance or equivalent as stated in contamination control strategy
+    <t xml:space="preserve">The post-oxidation DMF cooling-time test in the activation tank will be performed during the solvent run.
+Proposed completion date: 10/22/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-production acceptance of equipment-train rinse and swab cleanliness, or an equivalent criterion defined in the contamination control strategy
  生产前设备管线清洗/擦拭清洁度验收，或达到污染控制策略（contamination control strategy）中所述的同等标准</t>
   </si>
   <si>
-    <t xml:space="preserve">TOC testing for equipment train passivation has been completed. Solvent run with iodine will use test strips to verify cleanliness. </t>
-  </si>
-  <si>
-    <t>Investigation on contaminated sampling tool in the glovebox of L3 synthesizer SY16 and yellow solid contamination in the glovebox of L2 synthesizer SY15. Confirmation of contaminant ID is high recommended or at minimum the contamination must be confirmed to be limited to glovebox only, i.e., the possibility of contamination in the synthesizer must be ruled out.
+    <t xml:space="preserve">TOC testing for equipment-train passivation is complete. During the solvent run with iodine, cleanliness will be verified with test strips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investigation of the contaminated sampling tool in the glovebox of L3 synthesizer SY16, and of the yellow solid in the glovebox of L2 synthesizer SY15. Identification of the contaminant is strongly recommended. At a minimum, the contamination must be shown to be confined to the glovebox, and contamination inside the synthesizer must be ruled out.
 关于 L3 合成器 SY16 手套箱内采样工具被污染、以及 L2 合成器 SY15 手套箱内黄色固体污染的调查。强烈建议确认污染物身份（ID），或至少应确认污染仅限于手套箱内部，即必须排除合成器内部受到污染的可能性。</t>
   </si>
   <si>
